--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_02-02-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_02-02-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="169">
   <si>
     <t>SKU</t>
   </si>
@@ -181,27 +181,33 @@
     <t>£25.04</t>
   </si>
   <si>
+    <t>Error: ("Connection broken: ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None)", ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+  </si>
+  <si>
+    <t>£27.25</t>
+  </si>
+  <si>
+    <t>N/L</t>
+  </si>
+  <si>
+    <t>£33.83</t>
+  </si>
+  <si>
+    <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+  </si>
+  <si>
+    <t>£42.85</t>
+  </si>
+  <si>
+    <t>£41.67</t>
+  </si>
+  <si>
     <t>£27.69</t>
   </si>
   <si>
-    <t>£27.25</t>
-  </si>
-  <si>
-    <t>N/L</t>
-  </si>
-  <si>
-    <t>£33.83</t>
-  </si>
-  <si>
     <t>£41.61</t>
   </si>
   <si>
-    <t>£42.85</t>
-  </si>
-  <si>
-    <t>£41.67</t>
-  </si>
-  <si>
     <t>£11.50</t>
   </si>
   <si>
@@ -247,25 +253,28 @@
     <t>Add to Enquiry</t>
   </si>
   <si>
-    <t>Error: HTTPConnectionPool(host='localhost', port=49870): Read timed out. (read timeout=120)</t>
+    <t>£33.50</t>
+  </si>
+  <si>
+    <t>£47.08</t>
+  </si>
+  <si>
+    <t>£27.49</t>
   </si>
   <si>
     <t>£22.16</t>
   </si>
   <si>
-    <t>£47.08</t>
-  </si>
-  <si>
-    <t>£41.25</t>
-  </si>
-  <si>
-    <t>£27.49</t>
+    <t>£22.33</t>
   </si>
   <si>
     <t>£14.38</t>
   </si>
   <si>
-    <t>£16.01</t>
+    <t>£47.58</t>
+  </si>
+  <si>
+    <t>£25.63</t>
   </si>
   <si>
     <t>£10.15</t>
@@ -304,7 +313,7 @@
     <t>£33.20</t>
   </si>
   <si>
-    <t>£40.21</t>
+    <t>Timeout</t>
   </si>
   <si>
     <t>£39.69</t>
@@ -337,7 +346,7 @@
     <t>£31.66</t>
   </si>
   <si>
-    <t>£63.71</t>
+    <t>Cloudflare Blocked</t>
   </si>
   <si>
     <t>£62.8</t>
@@ -511,7 +520,7 @@
     <t>£67.76</t>
   </si>
   <si>
-    <t>Price Not Found</t>
+    <t>POA</t>
   </si>
 </sst>
 </file>
@@ -942,40 +951,40 @@
         <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N2" t="s">
         <v>57</v>
       </c>
       <c r="O2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P2" t="s">
         <v>57</v>
       </c>
       <c r="Q2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -995,40 +1004,40 @@
         <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="N3" t="s">
         <v>57</v>
       </c>
       <c r="O3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P3" t="s">
         <v>57</v>
       </c>
       <c r="Q3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -1048,40 +1057,40 @@
         <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="N4" t="s">
         <v>57</v>
       </c>
       <c r="O4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="P4" t="s">
         <v>57</v>
       </c>
       <c r="Q4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -1101,40 +1110,40 @@
         <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N5" t="s">
         <v>57</v>
       </c>
       <c r="O5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="P5" t="s">
         <v>57</v>
       </c>
       <c r="Q5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -1154,40 +1163,40 @@
         <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N6" t="s">
         <v>57</v>
       </c>
       <c r="O6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P6" t="s">
         <v>57</v>
       </c>
       <c r="Q6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -1207,40 +1216,40 @@
         <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N7" t="s">
         <v>57</v>
       </c>
       <c r="O7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="P7" t="s">
         <v>57</v>
       </c>
       <c r="Q7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1260,40 +1269,40 @@
         <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="M8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N8" t="s">
         <v>57</v>
       </c>
       <c r="O8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="P8" t="s">
         <v>57</v>
       </c>
       <c r="Q8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1316,37 +1325,37 @@
         <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N9" t="s">
         <v>57</v>
       </c>
       <c r="O9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="P9" t="s">
         <v>57</v>
       </c>
       <c r="Q9" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1360,46 +1369,46 @@
         <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K10" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="L10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s">
         <v>57</v>
       </c>
       <c r="O10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P10" t="s">
         <v>57</v>
       </c>
       <c r="Q10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1419,40 +1428,40 @@
         <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K11" t="s">
         <v>56</v>
       </c>
       <c r="L11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s">
         <v>57</v>
       </c>
       <c r="O11" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="P11" t="s">
         <v>57</v>
       </c>
       <c r="Q11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1472,25 +1481,25 @@
         <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J12" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K12" t="s">
         <v>57</v>
       </c>
       <c r="L12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M12" t="s">
         <v>57</v>
@@ -1499,7 +1508,7 @@
         <v>57</v>
       </c>
       <c r="O12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s">
         <v>57</v>
@@ -1525,40 +1534,40 @@
         <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s">
         <v>57</v>
       </c>
       <c r="O13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P13" t="s">
         <v>57</v>
       </c>
       <c r="Q13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1572,40 +1581,40 @@
         <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J14" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K14" t="s">
         <v>57</v>
       </c>
       <c r="L14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N14" t="s">
         <v>57</v>
       </c>
       <c r="O14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="P14" t="s">
         <v>57</v>
@@ -1631,34 +1640,34 @@
         <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N15" t="s">
         <v>57</v>
       </c>
       <c r="O15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="P15" t="s">
         <v>57</v>
@@ -1684,40 +1693,40 @@
         <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N16" t="s">
         <v>57</v>
       </c>
       <c r="O16" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="P16" t="s">
         <v>57</v>
       </c>
       <c r="Q16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
